--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119834847</v>
       </c>
       <c r="B2" t="n">
-        <v>86289</v>
+        <v>86306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86297</v>
+        <v>86314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86314</v>
+        <v>86163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson.</t>
+          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson. På barrmatta i annars örtrik, fuktig granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86163</v>
+        <v>86165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86165</v>
+        <v>86166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86166</v>
+        <v>86175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86200</v>
+        <v>86201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86201</v>
+        <v>86206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119834883</v>
       </c>
       <c r="B3" t="n">
-        <v>86206</v>
+        <v>86210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119834847</v>
       </c>
       <c r="B2" t="n">
-        <v>86306</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,53 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834883</v>
+        <v>96281942</v>
       </c>
       <c r="B3" t="n">
-        <v>86210</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248952</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Brandrud) Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Jmt</t>
+          <t>NA, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456241</v>
+        <v>455939</v>
       </c>
       <c r="R3" t="n">
-        <v>7189393</v>
+        <v>7189049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,17 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson. På barrmatta i annars örtrik, fuktig granskog.</t>
+          <t>West.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,26 +856,135 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119834883</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartåsen, Svartåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>456241</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7189393</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson. På barrmatta i annars örtrik, fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96281942</t>
         </is>
       </c>
     </row>
@@ -985,8 +1000,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96281942</v>
+        <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NA, Jmt</t>
+          <t>Svartåsen, Svartåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455939</v>
+        <v>456205</v>
       </c>
       <c r="R3" t="n">
-        <v>7189049</v>
+        <v>7189343</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>West.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,69 +867,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Alexander Singer, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96281942</t>
+          <t>https://artportalen.se/Sighting/136088304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834883</v>
+        <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>87204</v>
+        <v>91584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>248952</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartåsen, Svartåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456241</v>
+        <v>456232</v>
       </c>
       <c r="R4" t="n">
-        <v>7189393</v>
+        <v>7189384</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson. På barrmatta i annars örtrik, fuktig granskog.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,11 +962,6 @@
       </c>
       <c r="AE4" t="b">
         <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -991,16 +969,242 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136088477</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96281942</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>455939</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7189049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>West.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96281942</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119834883</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartåsen, Svartåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456241</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7189393</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bekräftad som barbaricus via mikroskopering av Erik Persson. På barrmatta i annars örtrik, fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119834883</t>
         </is>
@@ -1011,6 +1215,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
